--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92552754113</v>
+        <v>46157.93105776161</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93105776161</v>
+        <v>46157.93131539677</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93131539677</v>
+        <v>46157.93379538911</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93379538911</v>
+        <v>46157.93689894371</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93689894371</v>
+        <v>46158.28202866787</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28202866787</v>
+        <v>46158.29733273583</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29733273583</v>
+        <v>46158.29802122847</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29802122847</v>
+        <v>46158.33366489464</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33366489464</v>
+        <v>46158.37218355288</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_15-20-35/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37218355288</v>
+        <v>46158.37273445001</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
